--- a/xls/square_high_un_16_tri3_21.xlsx
+++ b/xls/square_high_un_16_tri3_21.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>598</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>340</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>485</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19">
+        <v>2676</v>
+      </c>
+      <c r="I19">
+        <v>-2.29372248352245</v>
+      </c>
+      <c r="J19">
+        <v>-1.9461406226738482</v>
+      </c>
+      <c r="K19">
+        <v>-0.05782692592682156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <v>598</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>340</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>564</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>3138</v>
+      </c>
+      <c r="I20">
+        <v>-0.7935718569372467</v>
+      </c>
+      <c r="J20">
+        <v>-0.7189885857294833</v>
+      </c>
+      <c r="K20">
+        <v>2.0826270834071674</v>
+      </c>
+    </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
         <v>11</v>
